--- a/artfynd/A 74070-2021 artfynd.xlsx
+++ b/artfynd/A 74070-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74070-2021 artfynd.xlsx
+++ b/artfynd/A 74070-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100212707</v>
+        <v>100212663</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420307.4488002524</v>
+        <v>420147</v>
       </c>
       <c r="R2" t="n">
-        <v>6840593.769719919</v>
+        <v>6840715</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100212681</v>
+        <v>100212677</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420350.8172760548</v>
+        <v>420165</v>
       </c>
       <c r="R3" t="n">
-        <v>6840783.126663809</v>
+        <v>6840671</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100212691</v>
+        <v>100212679</v>
       </c>
       <c r="B4" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420350.8172760548</v>
+        <v>420238</v>
       </c>
       <c r="R4" t="n">
-        <v>6840783.126663809</v>
+        <v>6840648</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100212704</v>
+        <v>100212691</v>
       </c>
       <c r="B5" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420252.9309845653</v>
+        <v>420351</v>
       </c>
       <c r="R5" t="n">
-        <v>6840621.142282316</v>
+        <v>6840783</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100212717</v>
+        <v>100212704</v>
       </c>
       <c r="B6" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420203.0184179955</v>
+        <v>420253</v>
       </c>
       <c r="R6" t="n">
-        <v>6840785.600564411</v>
+        <v>6840621</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100212727</v>
+        <v>100212717</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420392.1200702945</v>
+        <v>420203</v>
       </c>
       <c r="R7" t="n">
-        <v>6840533.893216114</v>
+        <v>6840785</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1260,7 @@
         <v>100212723</v>
       </c>
       <c r="B8" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420335.8745612658</v>
+        <v>420336</v>
       </c>
       <c r="R8" t="n">
-        <v>6840876.987503047</v>
+        <v>6840877</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100212651</v>
+        <v>100212742</v>
       </c>
       <c r="B9" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420446.3225367877</v>
+        <v>420201</v>
       </c>
       <c r="R9" t="n">
-        <v>6840986.457607008</v>
+        <v>6840631</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,35 +1422,19 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Urskogsartad myr</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1573,22 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Öster, John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100212726</v>
+        <v>100212748</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420393.5667748418</v>
+        <v>420298</v>
       </c>
       <c r="R10" t="n">
-        <v>6840473.093038383</v>
+        <v>6840332</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1519,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100212718</v>
+        <v>102380060</v>
       </c>
       <c r="B11" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,34 +1559,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420350.8172760548</v>
+        <v>420239</v>
       </c>
       <c r="R11" t="n">
-        <v>6840783.126663809</v>
+        <v>6840815</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,22 +1614,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,27 +1634,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100212749</v>
+        <v>102380091</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,34 +1657,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420350.8172760548</v>
+        <v>420297</v>
       </c>
       <c r="R12" t="n">
-        <v>6840783.126663809</v>
+        <v>6840828</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,22 +1712,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,27 +1732,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100212677</v>
+        <v>102380152</v>
       </c>
       <c r="B13" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,16 +1773,17 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>420165.1820424371</v>
+        <v>420361</v>
       </c>
       <c r="R13" t="n">
-        <v>6840671.123239174</v>
+        <v>6840815</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,22 +1810,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,27 +1830,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100212750</v>
+        <v>102380200</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,34 +1853,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420385.5264582845</v>
+        <v>420375</v>
       </c>
       <c r="R14" t="n">
-        <v>6840577.721132333</v>
+        <v>6840675</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,22 +1908,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,27 +1928,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100212679</v>
+        <v>102381864</v>
       </c>
       <c r="B15" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,16 +1969,17 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420237.8654226221</v>
+        <v>420525</v>
       </c>
       <c r="R15" t="n">
-        <v>6840648.075840708</v>
+        <v>6840712</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,22 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,27 +2026,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100212663</v>
+        <v>102381920</v>
       </c>
       <c r="B16" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,16 +2067,17 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420146.7232145971</v>
+        <v>420404</v>
       </c>
       <c r="R16" t="n">
-        <v>6840715.699971827</v>
+        <v>6840830</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,22 +2104,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,27 +2124,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100212742</v>
+        <v>102381949</v>
       </c>
       <c r="B17" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,16 +2165,17 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Härjedalen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420200.8471511824</v>
+        <v>420338</v>
       </c>
       <c r="R17" t="n">
-        <v>6840630.419644373</v>
+        <v>6840892</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,22 +2202,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,27 +2222,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100212664</v>
+        <v>100212681</v>
       </c>
       <c r="B18" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,21 +2245,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229569</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varglavsknöl</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phacopsis vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tul.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2269,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420361.6385292375</v>
+        <v>420351</v>
       </c>
       <c r="R18" t="n">
-        <v>6840408.316202063</v>
+        <v>6840783</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2549,19 +2302,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,51 +2331,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102380071</v>
+        <v>100212750</v>
       </c>
       <c r="B19" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420238.3982440244</v>
+        <v>420385</v>
       </c>
       <c r="R19" t="n">
-        <v>6840814.686650866</v>
+        <v>6840578</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,22 +2396,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,49 +2416,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102381920</v>
+        <v>102380052</v>
       </c>
       <c r="B20" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2464,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420403.243461651</v>
+        <v>420239</v>
       </c>
       <c r="R20" t="n">
-        <v>6840829.858438058</v>
+        <v>6840815</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,19 +2497,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,37 +2526,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102380091</v>
+        <v>102380106</v>
       </c>
       <c r="B21" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420297.194824327</v>
+        <v>420335</v>
       </c>
       <c r="R21" t="n">
-        <v>6840828.514946241</v>
+        <v>6840821</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,19 +2595,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,37 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102380152</v>
+        <v>102380287</v>
       </c>
       <c r="B22" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420360.5919279993</v>
+        <v>420490</v>
       </c>
       <c r="R22" t="n">
-        <v>6840815.180065152</v>
+        <v>6840550</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,19 +2693,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,15 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102380106</v>
+        <v>100212707</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3056,35 +2733,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420334.5787863467</v>
+        <v>420307</v>
       </c>
       <c r="R23" t="n">
-        <v>6840821.003721602</v>
+        <v>6840594</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,22 +2787,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,27 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102380052</v>
+        <v>102380090</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +2855,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420238.3982440244</v>
+        <v>420297</v>
       </c>
       <c r="R24" t="n">
-        <v>6840814.686650866</v>
+        <v>6840828</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,19 +2888,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,15 +2917,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102380060</v>
+        <v>100212727</v>
       </c>
       <c r="B25" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,35 +2928,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420238.3982440244</v>
+        <v>420392</v>
       </c>
       <c r="R25" t="n">
-        <v>6840814.686650866</v>
+        <v>6840534</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3337,22 +2982,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,27 +3002,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102380150</v>
+        <v>100212749</v>
       </c>
       <c r="B26" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,17 +3043,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420360.5919279993</v>
+        <v>420351</v>
       </c>
       <c r="R26" t="n">
-        <v>6840815.180065152</v>
+        <v>6840783</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3450,22 +3079,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,27 +3099,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102380226</v>
+        <v>102380150</v>
       </c>
       <c r="B27" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,21 +3122,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,10 +3147,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420375.4323454313</v>
+        <v>420361</v>
       </c>
       <c r="R27" t="n">
-        <v>6840675.74758888</v>
+        <v>6840815</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3566,19 +3180,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3605,51 +3209,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102381949</v>
+        <v>100212664</v>
       </c>
       <c r="B28" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>967</v>
+        <v>229569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Varglavsknöl</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Phacopsis vulpina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tul.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>420338.6017146882</v>
+        <v>420361</v>
       </c>
       <c r="R28" t="n">
-        <v>6840892.114401346</v>
+        <v>6840409</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,22 +3274,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,27 +3294,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102380262</v>
+        <v>100212651</v>
       </c>
       <c r="B29" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,17 +3335,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>420476.2301105213</v>
+        <v>420447</v>
       </c>
       <c r="R29" t="n">
-        <v>6840593.664155629</v>
+        <v>6840986</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3789,22 +3374,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,33 +3388,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102380090</v>
+        <v>100212718</v>
       </c>
       <c r="B30" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,35 +3423,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420297.194824327</v>
+        <v>420351</v>
       </c>
       <c r="R30" t="n">
-        <v>6840828.514946241</v>
+        <v>6840783</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3902,22 +3477,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,27 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102381864</v>
+        <v>100212726</v>
       </c>
       <c r="B31" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3960,35 +3520,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härjedalen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420524.6093105469</v>
+        <v>420394</v>
       </c>
       <c r="R31" t="n">
-        <v>6840712.175911614</v>
+        <v>6840473</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4015,22 +3574,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,27 +3594,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102380203</v>
+        <v>102380071</v>
       </c>
       <c r="B32" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,10 +3642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420375.4323454313</v>
+        <v>420239</v>
       </c>
       <c r="R32" t="n">
-        <v>6840675.74758888</v>
+        <v>6840815</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4131,19 +3675,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,12 +3707,7 @@
         <v>102380092</v>
       </c>
       <c r="B33" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4211,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420297.194824327</v>
+        <v>420297</v>
       </c>
       <c r="R33" t="n">
-        <v>6840828.514946241</v>
+        <v>6840828</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,19 +3773,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4280,6 +3799,202 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>102380203</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Härjedalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>420375</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6840675</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>102380262</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Härjedalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>420477</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6840594</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74070-2021 artfynd.xlsx
+++ b/artfynd/A 74070-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212677</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212704</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212717</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212723</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212742</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212748</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380091</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1839,6 +1899,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380152</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102381864</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2133,6 +2208,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102381920</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2231,6 +2311,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102381949</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2328,6 +2413,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212681</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2425,6 +2515,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212750</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380052</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380106</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380287</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212707</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2914,6 +3029,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380090</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3011,6 +3131,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212727</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3108,6 +3233,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212749</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380150</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212664</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3409,6 +3549,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212651</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3506,6 +3651,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212718</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3603,6 +3753,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212726</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3701,6 +3856,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380071</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3799,6 +3959,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380092</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3897,6 +4062,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380203</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,8 +4165,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102380262</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>